--- a/final_data_pipeline/output/311313longform_elec_options.xlsx
+++ b/final_data_pipeline/output/311313longform_elec_options.xlsx
@@ -618,7 +618,7 @@
         <v>49</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="L2">
         <v>8000</v>
@@ -633,10 +633,10 @@
         <v>1033540.390911294</v>
       </c>
       <c r="R2">
-        <v>1.424052774018944</v>
+        <v>1.523070892784755</v>
       </c>
       <c r="S2">
-        <v>1.509252539912917</v>
+        <v>1.622381208625714</v>
       </c>
       <c r="T2">
         <v>129.1925488639118</v>
@@ -671,7 +671,7 @@
         <v>50</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="L3">
         <v>8000</v>
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="L6">
         <v>8000</v>
@@ -865,7 +865,7 @@
         <v>49</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="L7">
         <v>8000</v>
@@ -880,10 +880,10 @@
         <v>1999.58903506598</v>
       </c>
       <c r="R7">
-        <v>1.424052774018944</v>
+        <v>1.32738293362297</v>
       </c>
       <c r="S7">
-        <v>1.509252539912917</v>
+        <v>1.399902772843707</v>
       </c>
       <c r="T7">
         <v>0.2499486293832475</v>
@@ -918,7 +918,7 @@
         <v>50</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="L8">
         <v>8000</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L9">
         <v>8000</v>
@@ -1012,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L10">
         <v>8000</v>
@@ -1027,10 +1027,10 @@
         <v>329553.7431346105</v>
       </c>
       <c r="R10">
-        <v>0.9194563882063882</v>
+        <v>0.9359630391213685</v>
       </c>
       <c r="S10">
-        <v>0.940668567807351</v>
+        <v>0.9581010400034263</v>
       </c>
       <c r="T10">
         <v>41.19421789182632</v>
@@ -1065,7 +1065,7 @@
         <v>50</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="L11">
         <v>8000</v>
@@ -1112,7 +1112,7 @@
         <v>50</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L12">
         <v>8000</v>
@@ -1159,7 +1159,7 @@
         <v>50</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L13">
         <v>8000</v>
@@ -1206,7 +1206,7 @@
         <v>50</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L14">
         <v>8000</v>
@@ -1253,7 +1253,7 @@
         <v>49</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L15">
         <v>8000</v>
@@ -1268,10 +1268,10 @@
         <v>13584.38203503639</v>
       </c>
       <c r="R15">
-        <v>0.9194563882063882</v>
+        <v>0.9337049960039765</v>
       </c>
       <c r="S15">
-        <v>0.940668567807351</v>
+        <v>0.9557151767570068</v>
       </c>
       <c r="T15">
         <v>1.698047754379549</v>
@@ -1600,7 +1600,7 @@
         <v>50</v>
       </c>
       <c r="K22">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L22">
         <v>8000</v>
@@ -1647,7 +1647,7 @@
         <v>49</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L23">
         <v>8000</v>
@@ -1662,10 +1662,10 @@
         <v>296480.9719889741</v>
       </c>
       <c r="R23">
-        <v>0.9194563882063882</v>
+        <v>0.9359630391213685</v>
       </c>
       <c r="S23">
-        <v>0.940668567807351</v>
+        <v>0.9581010400034263</v>
       </c>
       <c r="T23">
         <v>37.06012149862176</v>
@@ -1900,7 +1900,7 @@
         <v>49</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L28">
         <v>8000</v>
@@ -1915,10 +1915,10 @@
         <v>860858.965189144</v>
       </c>
       <c r="R28">
-        <v>1.424052774018944</v>
+        <v>1.473592088566053</v>
       </c>
       <c r="S28">
-        <v>1.509252539912917</v>
+        <v>1.565708370582976</v>
       </c>
       <c r="T28">
         <v>107.607370648643</v>
@@ -1953,7 +1953,7 @@
         <v>50</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L29">
         <v>8000</v>
@@ -2000,7 +2000,7 @@
         <v>50</v>
       </c>
       <c r="K30">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L30">
         <v>8000</v>
@@ -2341,7 +2341,7 @@
         <v>49</v>
       </c>
       <c r="K37">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L37">
         <v>8000</v>
@@ -2356,10 +2356,10 @@
         <v>11175.27744273596</v>
       </c>
       <c r="R37">
-        <v>0.9194563882063882</v>
+        <v>0.9337049960039765</v>
       </c>
       <c r="S37">
-        <v>0.940668567807351</v>
+        <v>0.9557151767570068</v>
       </c>
       <c r="T37">
         <v>1.396909680341995</v>
@@ -2394,7 +2394,7 @@
         <v>50</v>
       </c>
       <c r="K38">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L38">
         <v>8000</v>
